--- a/SAL_JIG/SAL_JIG_CS1_Echo_Demo/측정자료/echo_demo_color_info_250429.xlsx
+++ b/SAL_JIG/SAL_JIG_CS1_Echo_Demo/측정자료/echo_demo_color_info_250429.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\SAL_JIG\SAL_JIG_CS1_Echo_Demo\측정자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F428952-B5CE-4DC9-995A-9AB76459F6B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DC718A-41A5-41AF-9644-55C49C0F053C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{E7F389A4-D036-4905-9FA4-286AFB64E499}"/>
+    <workbookView xWindow="2900" yWindow="3170" windowWidth="21600" windowHeight="11180" xr2:uid="{E7F389A4-D036-4905-9FA4-286AFB64E499}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -267,6 +267,30 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -276,32 +300,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -654,177 +654,177 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="4"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="12"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="3">
         <v>20</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <v>17.5</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="3">
         <v>7.7</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="2" t="s">
+      <c r="C7" s="13"/>
+      <c r="D7" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="2" t="s">
+      <c r="E7" s="12"/>
+      <c r="F7" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="2" t="s">
+      <c r="G7" s="11"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="J7" s="4"/>
+      <c r="J7" s="12"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="6" t="s">
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="G8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B9" s="10"/>
-      <c r="C9" s="11" t="s">
+      <c r="B9" s="6"/>
+      <c r="C9" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="7">
         <v>0.29559999999999997</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="7">
         <v>0.14019999999999999</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B10" s="12"/>
-      <c r="C10" s="11" t="s">
+      <c r="B10" s="8"/>
+      <c r="C10" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="7">
         <v>0.63529999999999998</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="7">
         <v>0.32740000000000002</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.45">
-      <c r="B11" s="13"/>
-      <c r="C11" s="11" t="s">
+      <c r="B11" s="9"/>
+      <c r="C11" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="7">
         <v>0.15570000000000001</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="7">
         <v>7.7700000000000005E-2</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
     </row>
     <row r="12" spans="2:10" ht="16" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="7">
         <v>0.124</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="7">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
     </row>
     <row r="13" spans="2:10" ht="16" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="7">
         <v>0.14399999999999999</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="7">
         <v>0.35599999999999998</v>
       </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
     </row>
     <row r="14" spans="2:10" ht="16" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
